--- a/data/race_results.xlsx
+++ b/data/race_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1f49bcc976a33a18/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/darrenlin/Documents/GitHub/darrenlingit.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="165" documentId="8_{9D1D27B6-4D24-1541-ADD1-9CFBB164E228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07B35E9B-FEDA-9E45-9171-49CC50695C82}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA82705-DFF2-834B-A025-D182AE8C83EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16180" xr2:uid="{C2616345-B642-2745-A976-3EFA97E7CA60}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16140" xr2:uid="{C2616345-B642-2745-A976-3EFA97E7CA60}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="60">
   <si>
     <t>Name</t>
   </si>
@@ -140,17 +140,92 @@
     <t>Shoes</t>
   </si>
   <si>
-    <t>Asics Novablast 5</t>
-  </si>
-  <si>
     <t>Nike Pegasus 41</t>
+  </si>
+  <si>
+    <t>https://sites.chronotrack.com/event/93393/results/entry/80452047</t>
+  </si>
+  <si>
+    <t>Photo</t>
+  </si>
+  <si>
+    <t>Story</t>
+  </si>
+  <si>
+    <t>Photo Caption</t>
+  </si>
+  <si>
+    <t>../images/races/sm5k2025.jpeg</t>
+  </si>
+  <si>
+    <t>../images/races/rb5k2026.jpeg</t>
+  </si>
+  <si>
+    <t>Rose Bowl 5k</t>
+  </si>
+  <si>
+    <t>../images/races/la5k2026.jpeg</t>
+  </si>
+  <si>
+    <t>LA 5k</t>
+  </si>
+  <si>
+    <t>Santa Monica Classic 5k</t>
+  </si>
+  <si>
+    <t>../images/races/dimsum10k2026.jpeg</t>
+  </si>
+  <si>
+    <t>Dim Sum 10k</t>
+  </si>
+  <si>
+    <t>../images/races/sm10k2026.jpeg</t>
+  </si>
+  <si>
+    <t>Santa Monica Classic 10k</t>
+  </si>
+  <si>
+    <t>My first race and first 5k with my UCLA friends.</t>
+  </si>
+  <si>
+    <t>Back in Santa Monica to do another 10k with some more UCLA friends.</t>
+  </si>
+  <si>
+    <t>GPX File</t>
+  </si>
+  <si>
+    <t>data/race_route/Santa_Monica_Classic_5k.gpx</t>
+  </si>
+  <si>
+    <t>data/race_route/Rose_Bowl_5k.gpx</t>
+  </si>
+  <si>
+    <t>data/race_route/LA_5K.gpx</t>
+  </si>
+  <si>
+    <t>data/race_route/Dim_Sum_Then_Some_10K.gpx</t>
+  </si>
+  <si>
+    <t>data/race_route/Santa_Monica_Classic_10K.gpx</t>
+  </si>
+  <si>
+    <t>ASICS Novablast 5</t>
+  </si>
+  <si>
+    <t>The 5k race before the LA marathon (which I didn't run).</t>
+  </si>
+  <si>
+    <t>My second race and one of my favorite routes which ended in the iconic Rose Bowl.</t>
+  </si>
+  <si>
+    <t>My first 10k, which I did with my AbbVie intern friends. It was also the first time I ran through puddles and rain.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -160,6 +235,12 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -186,12 +267,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="46" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,267 +610,393 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A4AB51C-E835-D841-B833-F0FDF27F29E3}">
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.33203125" customWidth="1"/>
-    <col min="5" max="6" width="10.83203125" style="2"/>
+    <col min="1" max="1" width="27.33203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="4"/>
+    <col min="3" max="3" width="10.83203125" style="5"/>
+    <col min="4" max="4" width="10.83203125" style="4"/>
+    <col min="5" max="6" width="10.83203125" style="6"/>
+    <col min="7" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="5">
         <v>45907</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="6">
         <v>2.0266203703703703E-2</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="6">
         <v>6.5162037037037037E-3</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="4">
         <v>332</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="4">
         <v>1735</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="4">
         <v>40</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="4">
         <v>97</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="4">
         <v>260</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="4">
         <v>722</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="4">
         <v>1546</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5">
+        <v>46040</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6">
+        <v>2.1724537037037039E-2</v>
+      </c>
+      <c r="F3" s="6">
+        <v>6.9791666666666665E-3</v>
+      </c>
+      <c r="G3" s="4">
+        <v>277</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1234</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="4">
+        <v>29</v>
+      </c>
+      <c r="K3" s="4">
+        <v>61</v>
+      </c>
+      <c r="L3" s="4">
+        <v>335</v>
+      </c>
+      <c r="M3" s="4">
+        <v>483</v>
+      </c>
+      <c r="N3" s="4">
+        <v>11327</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5">
+        <v>46088</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="6">
+        <v>2.2638888888888889E-2</v>
+      </c>
+      <c r="F4" s="6">
+        <v>7.2800925925925923E-3</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1280</v>
+      </c>
+      <c r="H4" s="4">
+        <v>6250</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="4">
+        <v>126</v>
+      </c>
+      <c r="K4" s="4">
+        <v>331</v>
+      </c>
+      <c r="L4" s="4">
+        <v>1166</v>
+      </c>
+      <c r="M4" s="4">
+        <v>2558</v>
+      </c>
+      <c r="N4" s="4">
+        <v>52021</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="5">
+        <v>46235</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="6">
+        <v>4.2013888888888892E-2</v>
+      </c>
+      <c r="F5" s="6">
+        <v>6.7708333333333336E-3</v>
+      </c>
+      <c r="G5" s="4">
+        <v>242</v>
+      </c>
+      <c r="H5" s="4">
+        <v>523</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="4">
+        <v>47</v>
+      </c>
+      <c r="K5" s="4">
+        <v>85</v>
+      </c>
+      <c r="L5" s="4">
+        <v>174</v>
+      </c>
+      <c r="M5" s="4">
+        <v>295</v>
+      </c>
+      <c r="N5" s="4">
+        <v>4335</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="5">
+        <v>46278</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="6">
+        <v>4.1435185185185186E-2</v>
+      </c>
+      <c r="F6" s="6">
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1582</v>
+      </c>
+      <c r="H6" s="4">
+        <v>4583</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" s="4">
+        <v>160</v>
+      </c>
+      <c r="K6" s="4">
+        <v>313</v>
+      </c>
+      <c r="L6" s="4">
+        <v>1261</v>
+      </c>
+      <c r="M6" s="4">
+        <v>2363</v>
+      </c>
+      <c r="N6" s="4">
+        <v>4782</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="P6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="P2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1">
-        <v>46040</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="2">
-        <v>2.1724537037037039E-2</v>
-      </c>
-      <c r="F3" s="2">
-        <v>6.9791666666666665E-3</v>
-      </c>
-      <c r="G3">
-        <v>277</v>
-      </c>
-      <c r="H3">
-        <v>1234</v>
-      </c>
-      <c r="I3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3">
-        <v>29</v>
-      </c>
-      <c r="K3">
-        <v>61</v>
-      </c>
-      <c r="L3">
-        <v>335</v>
-      </c>
-      <c r="M3">
-        <v>483</v>
-      </c>
-      <c r="N3">
-        <v>11327</v>
-      </c>
-      <c r="O3" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1">
-        <v>46088</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="2">
-        <v>2.2638888888888889E-2</v>
-      </c>
-      <c r="F4" s="2">
-        <v>7.2800925925925923E-3</v>
-      </c>
-      <c r="G4">
-        <v>1280</v>
-      </c>
-      <c r="H4">
-        <v>6250</v>
-      </c>
-      <c r="I4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>126</v>
-      </c>
-      <c r="K4">
-        <v>331</v>
-      </c>
-      <c r="L4">
-        <v>1166</v>
-      </c>
-      <c r="M4">
-        <v>2558</v>
-      </c>
-      <c r="N4">
-        <v>52021</v>
-      </c>
-      <c r="O4" t="s">
-        <v>33</v>
-      </c>
-      <c r="P4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="1">
-        <v>46235</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2">
-        <v>4.2013888888888892E-2</v>
-      </c>
-      <c r="F5" s="2">
-        <v>6.7708333333333336E-3</v>
-      </c>
-      <c r="G5">
-        <v>242</v>
-      </c>
-      <c r="H5">
-        <v>523</v>
-      </c>
-      <c r="I5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J5">
+      <c r="R6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="S6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="K5">
-        <v>85</v>
-      </c>
-      <c r="L5">
-        <v>174</v>
-      </c>
-      <c r="M5">
-        <v>295</v>
-      </c>
-      <c r="N5">
-        <v>4335</v>
-      </c>
-      <c r="O5" t="s">
-        <v>33</v>
-      </c>
-      <c r="P5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>31</v>
+      <c r="T6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
